--- a/data/trans_camb/P6906-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6906-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 73,95</t>
+          <t>4,93; 74,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 38,66</t>
+          <t>-11,34; 35,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,99; -3,9</t>
+          <t>-27,85; -3,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 43,21</t>
+          <t>-15,04; 39,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 48,23</t>
+          <t>-10,46; 44,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 43,11</t>
+          <t>-14,75; 40,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 47,71</t>
+          <t>3,18; 49,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 30,75</t>
+          <t>-6,55; 32,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 29,22</t>
+          <t>-14,2; 25,53</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,56; 1318,53</t>
+          <t>8,32; 1264,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 691,01</t>
+          <t>-100,0; 690,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 759,94</t>
+          <t>-9,93; 725,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,7; 458,02</t>
+          <t>-51,82; 525,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 412,99</t>
+          <t>-100,0; 429,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 7,66</t>
+          <t>-16,85; 8,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 3,82</t>
+          <t>-19,53; 6,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 14,84</t>
+          <t>-20,82; 15,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 21,61</t>
+          <t>-8,64; 22,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 24,17</t>
+          <t>-9,1; 23,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 20,99</t>
+          <t>-12,08; 19,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 9,37</t>
+          <t>-10,09; 8,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 7,07</t>
+          <t>-12,27; 7,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 12,61</t>
+          <t>-11,67; 11,33</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 35,04</t>
+          <t>-51,67; 38,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-65,02; 19,32</t>
+          <t>-60,51; 29,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,39; 77,57</t>
+          <t>-68,65; 67,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 127,55</t>
+          <t>-30,77; 131,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 136,81</t>
+          <t>-32,18; 139,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 119,66</t>
+          <t>-43,23; 109,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 42,43</t>
+          <t>-33,19; 41,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 33,91</t>
+          <t>-39,78; 36,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,91; 56,66</t>
+          <t>-42,3; 51,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 11,0</t>
+          <t>-10,61; 12,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 12,61</t>
+          <t>-9,67; 13,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 10,78</t>
+          <t>-13,07; 10,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,34</t>
+          <t>-0,01; 31,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 22,55</t>
+          <t>-7,9; 21,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 17,9</t>
+          <t>-9,17; 17,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 15,61</t>
+          <t>-1,56; 16,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 12,5</t>
+          <t>-4,61; 14,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 10,69</t>
+          <t>-6,62; 10,18</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 64,95</t>
+          <t>-38,72; 74,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,79; 74,74</t>
+          <t>-36,53; 79,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-45,18; 63,28</t>
+          <t>-49,52; 59,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 225,0</t>
+          <t>-0,57; 225,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 173,56</t>
+          <t>-28,76; 162,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 135,51</t>
+          <t>-31,97; 125,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 91,77</t>
+          <t>-6,0; 92,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 70,31</t>
+          <t>-18,15; 86,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 62,52</t>
+          <t>-26,36; 59,92</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 19,41</t>
+          <t>-5,65; 22,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 14,93</t>
+          <t>-10,08; 14,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 7,07</t>
+          <t>-14,91; 7,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-27,19; 12,03</t>
+          <t>-28,09; 9,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 27,99</t>
+          <t>-13,89; 25,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 7,95</t>
+          <t>-26,94; 8,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 14,03</t>
+          <t>-9,09; 13,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 14,54</t>
+          <t>-7,34; 14,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 4,04</t>
+          <t>-15,55; 4,18</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 112,33</t>
+          <t>-20,53; 124,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,06; 87,2</t>
+          <t>-34,42; 82,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,69; 46,91</t>
+          <t>-52,88; 51,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,24; 82,35</t>
+          <t>-74,5; 59,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 186,75</t>
+          <t>-36,65; 149,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,47; 39,21</t>
+          <t>-67,88; 44,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 78,38</t>
+          <t>-31,04; 69,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 78,39</t>
+          <t>-26,19; 77,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 20,17</t>
+          <t>-51,62; 21,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 27,98</t>
+          <t>-6,98; 26,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 34,47</t>
+          <t>-2,43; 33,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 13,42</t>
+          <t>-14,45; 11,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 41,41</t>
+          <t>-11,91; 41,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,01; 54,95</t>
+          <t>-2,69; 51,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 38,16</t>
+          <t>-7,33; 38,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 26,33</t>
+          <t>-3,05; 25,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 35,47</t>
+          <t>7,9; 35,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 19,26</t>
+          <t>-3,3; 20,42</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 287,8</t>
+          <t>-36,44; 280,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 397,73</t>
+          <t>-17,51; 368,37</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 160,85</t>
+          <t>-58,95; 132,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-68,0; —</t>
+          <t>-68,08; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,98; —</t>
+          <t>-24,32; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,51; —</t>
+          <t>-22,51; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 264,01</t>
+          <t>-20,4; 252,49</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18,27; 356,03</t>
+          <t>26,54; 402,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 228,54</t>
+          <t>-15,05; 235,24</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 9,55</t>
+          <t>-3,41; 9,42</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 7,37</t>
+          <t>-5,53; 6,93</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 3,0</t>
+          <t>-9,5; 3,13</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 16,64</t>
+          <t>-1,48; 16,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,68; 19,31</t>
+          <t>2,42; 18,71</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 10,13</t>
+          <t>-5,74; 10,44</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,21; 10,55</t>
+          <t>0,21; 10,42</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,32; 10,4</t>
+          <t>-0,13; 10,11</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 4,9</t>
+          <t>-5,45; 4,59</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 45,57</t>
+          <t>-13,63; 47,86</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 36,23</t>
+          <t>-21,49; 34,02</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 14,6</t>
+          <t>-38,55; 17,02</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 94,27</t>
+          <t>-6,19; 95,64</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10,84; 111,27</t>
+          <t>8,55; 103,49</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 57,72</t>
+          <t>-21,78; 59,24</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,85; 51,52</t>
+          <t>0,85; 52,3</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>1,12; 50,55</t>
+          <t>-0,47; 51,44</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 24,0</t>
+          <t>-22,4; 22,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6906-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6906-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>7,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>-0,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 74,29</t>
+          <t>4,06; 71,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 35,32</t>
+          <t>-11,08; 36,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,85; -3,89</t>
+          <t>-27,75; -5,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 39,34</t>
+          <t>-14,83; 39,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 44,16</t>
+          <t>-9,49; 51,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 40,95</t>
+          <t>-14,7; 45,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 49,21</t>
+          <t>2,38; 46,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 32,02</t>
+          <t>-5,42; 31,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 25,53</t>
+          <t>-14,82; 22,14</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>-7,14%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,32; 1264,58</t>
+          <t>-4,4; 1122,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 690,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 725,97</t>
+          <t>-11,2; 652,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 525,91</t>
+          <t>-48,55; 538,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 429,28</t>
+          <t>-100,0; 400,77</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,15</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>1,84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 8,25</t>
+          <t>-16,03; 7,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 6,23</t>
+          <t>-20,88; 3,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 15,26</t>
+          <t>-16,72; 16,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 22,01</t>
+          <t>-7,3; 20,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 23,97</t>
+          <t>-9,52; 23,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 19,93</t>
+          <t>-12,52; 18,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 8,72</t>
+          <t>-9,53; 10,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 7,55</t>
+          <t>-12,18; 7,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 11,33</t>
+          <t>-11,52; 12,38</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-18,7%</t>
+          <t>-3,63%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-5,57%</t>
+          <t>-0,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 38,32</t>
+          <t>-51,31; 40,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,51; 29,17</t>
+          <t>-65,5; 13,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 67,14</t>
+          <t>-54,73; 69,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 131,57</t>
+          <t>-27,23; 119,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 139,14</t>
+          <t>-34,36; 126,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 109,91</t>
+          <t>-43,56; 112,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 41,63</t>
+          <t>-32,28; 48,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 36,54</t>
+          <t>-39,8; 36,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,3; 51,34</t>
+          <t>-38,72; 55,76</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-2,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>0,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 12,1</t>
+          <t>-10,78; 11,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 13,05</t>
+          <t>-8,94; 13,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 10,11</t>
+          <t>-13,3; 8,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 31,08</t>
+          <t>0,69; 30,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 21,53</t>
+          <t>-9,55; 21,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 17,38</t>
+          <t>-7,0; 18,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 16,3</t>
+          <t>-3,51; 15,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 14,07</t>
+          <t>-4,82; 12,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 10,18</t>
+          <t>-7,79; 9,37</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-5,53%</t>
+          <t>-9,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 74,83</t>
+          <t>-40,83; 69,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 79,36</t>
+          <t>-34,76; 81,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 59,74</t>
+          <t>-50,91; 50,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 225,67</t>
+          <t>-0,39; 228,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 162,17</t>
+          <t>-30,84; 161,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,97; 125,22</t>
+          <t>-25,5; 148,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 92,67</t>
+          <t>-14,55; 88,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 86,76</t>
+          <t>-19,28; 68,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,36; 59,92</t>
+          <t>-31,09; 51,65</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,48</t>
+          <t>-2,42</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,0</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-0,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 22,08</t>
+          <t>-6,51; 20,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 14,83</t>
+          <t>-12,03; 14,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 7,96</t>
+          <t>-14,23; 9,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 9,56</t>
+          <t>-27,8; 10,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 25,87</t>
+          <t>-12,83; 26,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,94; 8,86</t>
+          <t>-18,53; 14,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 13,3</t>
+          <t>-10,05; 13,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 14,79</t>
+          <t>-6,7; 15,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 4,18</t>
+          <t>-10,11; 7,96</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-19,09%</t>
+          <t>-10,33%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-25,37%</t>
+          <t>-2,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-18,64%</t>
+          <t>-1,81%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,53; 124,64</t>
+          <t>-22,22; 123,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 82,19</t>
+          <t>-44,35; 79,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 51,3</t>
+          <t>-49,89; 55,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,5; 59,46</t>
+          <t>-73,34; 74,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 149,2</t>
+          <t>-32,96; 176,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,88; 44,39</t>
+          <t>-43,7; 100,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 69,74</t>
+          <t>-34,29; 68,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 77,28</t>
+          <t>-23,1; 86,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 21,69</t>
+          <t>-33,66; 40,87</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>22,57</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,85</t>
+          <t>9,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 26,43</t>
+          <t>-7,89; 27,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 33,82</t>
+          <t>-2,14; 34,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 11,3</t>
+          <t>-14,78; 11,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 41,24</t>
+          <t>-12,6; 42,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 51,81</t>
+          <t>0,63; 54,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 38,03</t>
+          <t>-6,32; 37,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 25,84</t>
+          <t>-1,86; 26,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,9; 35,86</t>
+          <t>6,7; 35,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 20,42</t>
+          <t>-1,64; 20,39</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-4,97%</t>
+          <t>-2,56%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>148,99%</t>
+          <t>154,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>59,38%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,44; 280,44</t>
+          <t>-36,0; 289,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 368,37</t>
+          <t>-14,45; 367,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 132,57</t>
+          <t>-59,93; 143,11</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-68,08; —</t>
+          <t>-67,75; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,32; —</t>
+          <t>-10,2; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,51; —</t>
+          <t>-18,58; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 252,49</t>
+          <t>-12,36; 277,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26,54; 402,42</t>
+          <t>27,9; 403,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 235,24</t>
+          <t>-8,01; 227,64</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 9,42</t>
+          <t>-2,47; 9,86</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 6,93</t>
+          <t>-5,1; 7,65</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 3,13</t>
+          <t>-8,54; 3,63</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 16,53</t>
+          <t>-0,37; 15,94</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,42; 18,71</t>
+          <t>3,18; 19,01</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 10,44</t>
+          <t>-1,44; 12,83</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,21; 10,42</t>
+          <t>0,02; 9,98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 10,11</t>
+          <t>0,24; 10,14</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 4,59</t>
+          <t>-2,86; 6,25</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-15,97%</t>
+          <t>-10,96%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-0,63%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 47,86</t>
+          <t>-10,88; 48,34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 34,02</t>
+          <t>-19,97; 37,24</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 17,02</t>
+          <t>-34,33; 18,51</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 95,64</t>
+          <t>-2,94; 89,47</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,55; 103,49</t>
+          <t>11,75; 106,57</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 59,24</t>
+          <t>-5,81; 73,3</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,85; 52,3</t>
+          <t>0,11; 50,41</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 51,44</t>
+          <t>1,01; 49,18</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 22,81</t>
+          <t>-11,95; 30,36</t>
         </is>
       </c>
     </row>
